--- a/docs/public/exam/2018-shang-1.xlsx
+++ b/docs/public/exam/2018-shang-1.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="8925" windowHeight="10455"/>
+    <workbookView windowWidth="6760" windowHeight="17080"/>
   </bookViews>
   <sheets>
     <sheet name="2016年上半年" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2016年上半年'!$A$1:$F$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2016年上半年'!$A$1:$G$80</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="14">
   <si>
     <t>序号</t>
   </si>
@@ -44,10 +44,10 @@
     <t>C</t>
   </si>
   <si>
-    <t>B</t>
+    <t>D</t>
   </si>
   <si>
-    <t>D</t>
+    <t>B</t>
   </si>
   <si>
     <t>D*</t>
@@ -84,7 +84,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,17 +106,7 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -132,6 +122,22 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -628,137 +634,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -780,6 +786,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -789,40 +804,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1357,18 +1369,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G80"/>
-  <sheetFormatPr defaultColWidth="9.8141592920354" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="9.8141592920354" style="2"/>
-    <col min="3" max="3" width="11.7522123893805" customWidth="1"/>
-    <col min="4" max="4" width="5.1858407079646" customWidth="1"/>
-    <col min="5" max="5" width="10.2743362831858"/>
-    <col min="6" max="6" width="16.5663716814159" customWidth="1"/>
+    <col min="2" max="2" width="9.81818181818182" style="2"/>
+    <col min="3" max="3" width="11.7545454545455" customWidth="1"/>
+    <col min="4" max="4" width="5.18181818181818" customWidth="1"/>
+    <col min="5" max="5" width="10.2727272727273"/>
+    <col min="6" max="6" width="16.5636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:6">
+    <row r="1" ht="15" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1384,1114 +1396,1272 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" ht="14.25" spans="1:6">
-      <c r="A2" s="3">
+    <row r="2" ht="15" hidden="1" spans="1:6">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="7" t="str">
+      <c r="B2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="9" t="str">
         <f>IF(AND(B2="",C2=""),"假",IF(B2=C2,"真","假"))</f>
         <v>假</v>
       </c>
-      <c r="E2" s="6"/>
+      <c r="E2" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" ht="14.25" spans="1:6">
+    <row r="3" ht="15" spans="1:6">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="7" t="str">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="10" t="str">
         <f t="shared" ref="D3:D34" si="0">IF(AND(B3="",C3=""),"假",IF(B3=C3,"真","假"))</f>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" ht="14.25" spans="1:6">
+    <row r="4" ht="15" spans="1:6">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="7" t="str">
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" ht="14.25" spans="1:6">
-      <c r="A5" s="8">
+    <row r="5" ht="15" spans="1:6">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="7" t="str">
+      <c r="B5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" s="1" customFormat="1" ht="14.25" spans="1:6">
-      <c r="A6" s="8">
+    <row r="6" s="1" customFormat="1" ht="15" hidden="1" spans="1:6">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="7" t="str">
+      <c r="B6" s="13"/>
+      <c r="C6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="9" t="str">
         <f>IF(AND(B7="",C6=""),"假",IF(B7=C6,"真","假"))</f>
         <v>假</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-    </row>
-    <row r="7" ht="14.25" spans="1:6">
-      <c r="A7" s="12">
+      <c r="E6" s="6">
+        <v>20261007</v>
+      </c>
+      <c r="F6" s="14"/>
+    </row>
+    <row r="7" ht="15" hidden="1" spans="1:6">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="7" t="str">
+      <c r="C7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="9" t="str">
         <f>IF(AND(B8="",C7=""),"假",IF(B8=C7,"真","假"))</f>
         <v>假</v>
       </c>
-      <c r="E7" s="6"/>
+      <c r="E7" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" ht="14.25" spans="1:6">
-      <c r="A8" s="8">
+    <row r="8" ht="15" spans="1:6">
+      <c r="A8" s="11">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="7" t="str">
+      <c r="B8" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" ht="14.25" spans="1:6">
-      <c r="A9" s="12">
+    <row r="9" ht="15" spans="1:6">
+      <c r="A9" s="15">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="7" t="str">
+      <c r="B9" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" ht="14.25" spans="1:6">
-      <c r="A10" s="8">
+    <row r="10" ht="15" spans="1:6">
+      <c r="A10" s="11">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="7" t="str">
+      <c r="C10" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" ht="14.25" spans="1:6">
-      <c r="A11" s="8">
+    <row r="11" ht="15" hidden="1" spans="1:6">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="7" t="str">
+      <c r="C11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" ht="14.25" spans="1:6">
-      <c r="A12" s="12">
+    <row r="12" ht="15" spans="1:6">
+      <c r="A12" s="15">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="7" t="str">
+      <c r="C12" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" ht="14.25" spans="1:6">
-      <c r="A13" s="8">
+    <row r="13" ht="15" hidden="1" spans="1:6">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="7" t="str">
+      <c r="C13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" ht="14.25" spans="1:6">
-      <c r="A14" s="8">
+    <row r="14" ht="15" hidden="1" spans="1:6">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="7" t="str">
+      <c r="C14" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" ht="14.25" spans="1:6">
-      <c r="A15" s="8">
+    <row r="15" ht="15" hidden="1" spans="1:6">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="7" t="str">
+      <c r="C15" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" ht="14.25" spans="1:6">
-      <c r="A16" s="8">
+    <row r="16" ht="15" hidden="1" spans="1:6">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="7" t="str">
+      <c r="C16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" ht="14.25" spans="1:6">
-      <c r="A17" s="8">
+    <row r="17" ht="15" hidden="1" spans="1:6">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="7" t="str">
+      <c r="B17" s="16"/>
+      <c r="C17" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="9" t="str">
         <f t="shared" ref="D17:D19" si="1">IF(AND(B18="",C17=""),"假",IF(B18=C17,"真","假"))</f>
         <v>假</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" ht="14.25" spans="1:6">
-      <c r="A18" s="8">
+    <row r="18" ht="15" hidden="1" spans="1:6">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="7" t="str">
+      <c r="B18" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="9" t="str">
         <f t="shared" si="1"/>
         <v>假</v>
       </c>
-      <c r="E18" s="6"/>
+      <c r="E18" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" ht="14.25" spans="1:6">
-      <c r="A19" s="8">
+    <row r="19" ht="15" hidden="1" spans="1:6">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="7" t="str">
+      <c r="B19" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="9" t="str">
         <f t="shared" si="1"/>
         <v>假</v>
       </c>
-      <c r="E19" s="6"/>
+      <c r="E19" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" ht="14.25" spans="1:6">
-      <c r="A20" s="8">
+    <row r="20" ht="15" hidden="1" spans="1:6">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="7" t="str">
+      <c r="C20" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E20" s="6"/>
+      <c r="E20" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" ht="14.25" spans="1:6">
-      <c r="A21" s="8">
+    <row r="21" ht="15" spans="1:6">
+      <c r="A21" s="11">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="7" t="str">
+      <c r="C21" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" ht="14.25" spans="1:6">
-      <c r="A22" s="12">
+    <row r="22" ht="15" spans="1:6">
+      <c r="A22" s="15">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="7" t="str">
+      <c r="B22" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" ht="14.25" spans="1:7">
-      <c r="A23" s="12">
+    <row r="23" ht="15" spans="1:7">
+      <c r="A23" s="15">
         <v>22</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="22"/>
+    </row>
+    <row r="24" ht="15" spans="1:7">
+      <c r="A24" s="15">
+        <v>23</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>真</v>
+      </c>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="22"/>
+    </row>
+    <row r="25" ht="15" spans="1:7">
+      <c r="A25" s="15">
+        <v>24</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="17" t="str">
+      <c r="C25" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
-      </c>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="19"/>
-    </row>
-    <row r="24" ht="14.25" spans="1:7">
-      <c r="A24" s="12">
-        <v>23</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="17" t="str">
+        <v>真</v>
+      </c>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="22"/>
+    </row>
+    <row r="26" ht="15" spans="1:6">
+      <c r="A26" s="15">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
-      </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="19"/>
-    </row>
-    <row r="25" ht="14.25" spans="1:7">
-      <c r="A25" s="12">
-        <v>24</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v>假</v>
-      </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="19"/>
-    </row>
-    <row r="26" ht="14.25" spans="1:6">
-      <c r="A26" s="12">
-        <v>25</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" ht="14.25" spans="1:6">
-      <c r="A27" s="8">
+    <row r="27" ht="15" hidden="1" spans="1:6">
+      <c r="A27" s="7">
         <v>26</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="7" t="str">
+      <c r="B27" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E27" s="6"/>
+      <c r="E27" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" ht="14.25" spans="1:6">
-      <c r="A28" s="8">
+    <row r="28" ht="15" spans="1:6">
+      <c r="A28" s="11">
         <v>27</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="7" t="str">
+      <c r="B28" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" ht="14.25" spans="1:6">
-      <c r="A29" s="8">
+    <row r="29" ht="15" spans="1:6">
+      <c r="A29" s="11">
         <v>28</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="7" t="str">
+      <c r="B29" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" s="1" customFormat="1" ht="14.25" spans="1:6">
-      <c r="A30" s="12">
+    <row r="30" s="1" customFormat="1" ht="15" hidden="1" spans="1:6">
+      <c r="A30" s="7">
         <v>29</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="7" t="str">
+      <c r="C30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-    </row>
-    <row r="31" ht="14.25" spans="1:6">
-      <c r="A31" s="8">
+      <c r="E30" s="6">
+        <v>20261007</v>
+      </c>
+      <c r="F30" s="14"/>
+    </row>
+    <row r="31" ht="15" hidden="1" spans="1:6">
+      <c r="A31" s="7">
         <v>30</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="7" t="str">
+      <c r="C31" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E31" s="6"/>
+      <c r="E31" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" ht="14.25" spans="1:6">
-      <c r="A32" s="8">
+    <row r="32" ht="15" hidden="1" spans="1:6">
+      <c r="A32" s="7">
         <v>31</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="7" t="str">
+      <c r="D32" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
-      <c r="E32" s="6"/>
+      <c r="E32" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" ht="14.25" spans="1:6">
-      <c r="A33" s="12">
+    <row r="33" ht="15" spans="1:6">
+      <c r="A33" s="15">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="7" t="str">
+      <c r="B33" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>假</v>
+        <v>真</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" ht="14.25" spans="1:6">
-      <c r="A34" s="12">
+    <row r="34" ht="15" spans="1:6">
+      <c r="A34" s="7">
         <v>33</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="7" t="str">
+      <c r="C34" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="9" t="str">
         <f t="shared" si="0"/>
         <v>假</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" ht="14.25" spans="1:6">
-      <c r="A35" s="12">
+    <row r="35" ht="15" spans="1:6">
+      <c r="A35" s="7">
         <v>34</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="7" t="str">
+      <c r="B35" s="7"/>
+      <c r="C35" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="9" t="str">
         <f t="shared" ref="D35:D76" si="2">IF(AND(B35="",C35=""),"假",IF(B35=C35,"真","假"))</f>
         <v>假</v>
       </c>
-      <c r="E35" s="6"/>
+      <c r="E35" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" ht="14.25" spans="1:6">
-      <c r="A36" s="8">
+    <row r="36" ht="15" spans="1:6">
+      <c r="A36" s="7">
         <v>35</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
-      </c>
-      <c r="E36" s="6"/>
+      <c r="B36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>假</v>
+      </c>
+      <c r="E36" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" ht="14.25" spans="1:6">
-      <c r="A37" s="8">
+    <row r="37" ht="15" spans="1:6">
+      <c r="A37" s="7">
         <v>36</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
-      </c>
-      <c r="E37" s="6"/>
+      <c r="B37" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>假</v>
+      </c>
+      <c r="E37" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" ht="14.25" spans="1:6">
-      <c r="A38" s="8">
+    <row r="38" ht="15" spans="1:6">
+      <c r="A38" s="11">
         <v>37</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="C38" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" ht="14.25" spans="1:6">
-      <c r="A39" s="8">
+    <row r="39" ht="15" spans="1:6">
+      <c r="A39" s="11">
         <v>38</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="B39" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" ht="14.25" spans="1:6">
-      <c r="A40" s="8">
+    <row r="40" ht="15" spans="1:6">
+      <c r="A40" s="11">
         <v>39</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="B40" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" ht="14.25" spans="1:6">
-      <c r="A41" s="8">
+    <row r="41" ht="15" spans="1:6">
+      <c r="A41" s="11">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="B41" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" ht="14.25" spans="1:6">
-      <c r="A42" s="8">
+    <row r="42" ht="15" spans="1:6">
+      <c r="A42" s="11">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="B42" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" ht="14.25" spans="1:6">
-      <c r="A43" s="8">
+    <row r="43" ht="15" spans="1:6">
+      <c r="A43" s="11">
         <v>42</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="C43" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" ht="14.25" spans="1:6">
-      <c r="A44" s="8">
+    <row r="44" ht="15" spans="1:6">
+      <c r="A44" s="11">
         <v>43</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="B44" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" ht="14.25" spans="1:6">
-      <c r="A45" s="12">
+    <row r="45" ht="15" spans="1:6">
+      <c r="A45" s="7">
         <v>44</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="7" t="str">
+      <c r="D45" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" ht="14.25" spans="1:6">
-      <c r="A46" s="8">
+    <row r="46" ht="15" spans="1:6">
+      <c r="A46" s="11">
         <v>45</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="9"/>
-      <c r="D46" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="C46" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" ht="14.25" spans="1:6">
-      <c r="A47" s="8">
+    <row r="47" ht="15" spans="1:6">
+      <c r="A47" s="11">
         <v>46</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="B47" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" ht="14.25" spans="1:6">
-      <c r="A48" s="8">
+    <row r="48" ht="15" spans="1:6">
+      <c r="A48" s="11">
         <v>47</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="C48" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" ht="14.25" spans="1:6">
-      <c r="A49" s="8">
+    <row r="49" ht="15" spans="1:6">
+      <c r="A49" s="11">
         <v>48</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="C49" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" ht="14.25" spans="1:6">
-      <c r="A50" s="8">
+    <row r="50" ht="15" spans="1:6">
+      <c r="A50" s="7">
         <v>49</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="7" t="str">
+      <c r="C50" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
     </row>
-    <row r="51" ht="14.25" spans="1:6">
-      <c r="A51" s="8">
+    <row r="51" ht="15" spans="1:6">
+      <c r="A51" s="7">
         <v>50</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="7" t="str">
+      <c r="C51" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
     </row>
-    <row r="52" ht="14.25" spans="1:6">
-      <c r="A52" s="8">
+    <row r="52" ht="15" spans="1:6">
+      <c r="A52" s="7">
         <v>51</v>
       </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="7" t="str">
+      <c r="B52" s="7"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
     </row>
-    <row r="53" ht="14.25" spans="1:6">
-      <c r="A53" s="8">
+    <row r="53" ht="15" spans="1:6">
+      <c r="A53" s="7">
         <v>52</v>
       </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="7" t="str">
+      <c r="B53" s="7"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
     </row>
-    <row r="54" ht="14.25" spans="1:6">
-      <c r="A54" s="8">
+    <row r="54" ht="15" spans="1:6">
+      <c r="A54" s="7">
         <v>53</v>
       </c>
-      <c r="B54" s="8"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="7" t="str">
+      <c r="B54" s="7"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
     </row>
-    <row r="55" ht="14.25" spans="1:6">
-      <c r="A55" s="8">
+    <row r="55" ht="15" spans="1:6">
+      <c r="A55" s="7">
         <v>54</v>
       </c>
-      <c r="B55" s="8"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="7" t="str">
+      <c r="B55" s="7"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" ht="14.25" spans="1:6">
-      <c r="A56" s="8">
+    <row r="56" ht="15" spans="1:6">
+      <c r="A56" s="7">
         <v>55</v>
       </c>
-      <c r="B56" s="8"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="7" t="str">
+      <c r="B56" s="7"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" ht="14.25" spans="1:6">
-      <c r="A57" s="8">
+    <row r="57" ht="15" spans="1:6">
+      <c r="A57" s="7">
         <v>56</v>
       </c>
-      <c r="B57" s="8"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="7" t="str">
+      <c r="B57" s="7"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" ht="14.25" spans="1:6">
-      <c r="A58" s="8">
+    <row r="58" ht="15" spans="1:6">
+      <c r="A58" s="7">
         <v>57</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="7" t="str">
+      <c r="C58" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" ht="14.25" spans="1:6">
-      <c r="A59" s="8">
+    <row r="59" ht="15" spans="1:6">
+      <c r="A59" s="7">
         <v>58</v>
       </c>
-      <c r="B59" s="8"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="7" t="str">
+      <c r="B59" s="7"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
     </row>
-    <row r="60" ht="14.25" spans="1:6">
-      <c r="A60" s="8">
+    <row r="60" ht="15" spans="1:6">
+      <c r="A60" s="7">
         <v>59</v>
       </c>
-      <c r="B60" s="8"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="7" t="str">
+      <c r="B60" s="7"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
     </row>
-    <row r="61" ht="14.25" spans="1:6">
-      <c r="A61" s="8">
+    <row r="61" ht="15" spans="1:6">
+      <c r="A61" s="7">
         <v>60</v>
       </c>
-      <c r="B61" s="8"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="7" t="str">
+      <c r="B61" s="7"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
     </row>
-    <row r="62" ht="14.25" spans="1:6">
-      <c r="A62" s="8">
+    <row r="62" ht="15" spans="1:6">
+      <c r="A62" s="7">
         <v>61</v>
       </c>
-      <c r="B62" s="8"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="7" t="str">
+      <c r="B62" s="7"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" ht="14.25" spans="1:6">
-      <c r="A63" s="8">
+    <row r="63" ht="15" spans="1:6">
+      <c r="A63" s="7">
         <v>62</v>
       </c>
-      <c r="B63" s="8"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="7" t="str">
+      <c r="B63" s="7"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" ht="14.25" spans="1:6">
-      <c r="A64" s="8">
+    <row r="64" ht="15" spans="1:6">
+      <c r="A64" s="7">
         <v>63</v>
       </c>
-      <c r="B64" s="8"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="7" t="str">
+      <c r="B64" s="7"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" ht="14.25" spans="1:6">
-      <c r="A65" s="8">
+    <row r="65" ht="15" spans="1:6">
+      <c r="A65" s="7">
         <v>64</v>
       </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="7" t="str">
+      <c r="B65" s="7"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" ht="14.25" spans="1:6">
-      <c r="A66" s="8">
+    <row r="66" ht="15" spans="1:6">
+      <c r="A66" s="7">
         <v>65</v>
       </c>
-      <c r="C66" s="9"/>
-      <c r="D66" s="7" t="str">
+      <c r="B66" s="13"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="9" t="str">
         <f>IF(AND(B68="",C66=""),"假",IF(B68=C66,"真","假"))</f>
         <v>假</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" s="1" customFormat="1" ht="14.25" spans="1:6">
-      <c r="A67" s="8">
+    <row r="67" s="1" customFormat="1" ht="15" spans="1:6">
+      <c r="A67" s="11">
         <v>66</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C67" s="9"/>
-      <c r="D67" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
-      </c>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-    </row>
-    <row r="68" s="1" customFormat="1" ht="14.25" spans="1:6">
-      <c r="A68" s="8">
+      <c r="B67" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
+      </c>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="15" spans="1:6">
+      <c r="A68" s="11">
         <v>67</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" s="9"/>
-      <c r="D68" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
-      </c>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-    </row>
-    <row r="69" ht="14.25" spans="1:6">
-      <c r="A69" s="8">
+      <c r="B68" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
+      </c>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+    </row>
+    <row r="69" ht="15" spans="1:6">
+      <c r="A69" s="11">
         <v>68</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C69" s="9"/>
-      <c r="D69" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="B69" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" ht="14.25" spans="1:6">
-      <c r="A70" s="8">
+    <row r="70" ht="15" spans="1:6">
+      <c r="A70" s="11">
         <v>69</v>
       </c>
-      <c r="B70" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C70" s="9"/>
-      <c r="D70" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
+      <c r="B70" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>真</v>
       </c>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" ht="14.25" spans="1:6">
-      <c r="A71" s="8">
+    <row r="71" ht="15" spans="1:6">
+      <c r="A71" s="7">
         <v>70</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="9"/>
-      <c r="D71" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>假</v>
-      </c>
-      <c r="E71" s="6"/>
+      <c r="C71" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>假</v>
+      </c>
+      <c r="E71" s="6">
+        <v>20261007</v>
+      </c>
       <c r="F71" s="6"/>
     </row>
-    <row r="72" ht="14.25" spans="1:6">
-      <c r="A72" s="8">
+    <row r="72" ht="15" spans="1:6">
+      <c r="A72" s="7">
         <v>71</v>
       </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="7" t="str">
+      <c r="B72" s="7"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" ht="14.25" spans="1:6">
-      <c r="A73" s="8">
+    <row r="73" ht="15" spans="1:6">
+      <c r="A73" s="7">
         <v>72</v>
       </c>
-      <c r="B73" s="8"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="7" t="str">
+      <c r="B73" s="7"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
     </row>
-    <row r="74" ht="14.25" spans="1:6">
-      <c r="A74" s="8">
+    <row r="74" ht="15" spans="1:6">
+      <c r="A74" s="7">
         <v>73</v>
       </c>
-      <c r="B74" s="8"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="7" t="str">
+      <c r="B74" s="7"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" ht="14.25" spans="1:6">
-      <c r="A75" s="8">
+    <row r="75" ht="15" spans="1:6">
+      <c r="A75" s="7">
         <v>74</v>
       </c>
-      <c r="B75" s="8"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="7" t="str">
+      <c r="B75" s="7"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" ht="14.25" spans="1:6">
-      <c r="A76" s="8">
+    <row r="76" ht="15" spans="1:6">
+      <c r="A76" s="7">
         <v>75</v>
       </c>
-      <c r="B76" s="8"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="7" t="str">
+      <c r="B76" s="7"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="9" t="str">
         <f t="shared" si="2"/>
         <v>假</v>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
     </row>
-    <row r="78" ht="13.85" spans="1:2">
+    <row r="78" ht="14.5" spans="1:2">
       <c r="A78" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B78" s="20">
+      <c r="B78" s="23">
         <f>COUNTA(B2:B74)</f>
         <v>53</v>
       </c>
     </row>
-    <row r="79" ht="13.85" spans="1:2">
+    <row r="79" ht="14.5" spans="1:2">
       <c r="A79" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B79" s="20">
+      <c r="B79" s="23">
         <f>COUNTIF(D4:D76,"真")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" ht="13.85" spans="1:2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" ht="14.5" spans="1:1">
       <c r="A80" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B80" s="21"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G80" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="4">
+      <filters blank="1"/>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
